--- a/hfa_default_indicators.xlsx
+++ b/hfa_default_indicators.xlsx
@@ -781,19 +781,19 @@
         <v>variantGroupId</v>
       </c>
       <c r="M1" t="str">
-        <v>r_code__Round 1</v>
+        <v>code__Round 1</v>
       </c>
       <c r="N1" t="str">
-        <v>r_filter_code__Round 1</v>
+        <v>filter_code__Round 1</v>
       </c>
       <c r="O1" t="str">
-        <v>r_variant_code__mobile_strategy__Round 1</v>
+        <v>variant_code__mobile_strategy__Round 1</v>
       </c>
       <c r="P1" t="str">
-        <v>r_variant_code__fixed_strategy__Round 1</v>
+        <v>variant_code__fixed_strategy__Round 1</v>
       </c>
       <c r="Q1" t="str">
-        <v>r_variant_code__mobile_and_fixed_strategy__Round 1</v>
+        <v>variant_code__mobile_and_fixed_strategy__Round 1</v>
       </c>
     </row>
     <row r="2">
